--- a/feature/fix-participant-status/ig/ValueSet-sas-valueset-typeidentifiant.xlsx
+++ b/feature/fix-participant-status/ig/ValueSet-sas-valueset-typeidentifiant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:59:14+00:00</t>
+    <t>2026-06-15T13:11:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
